--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/VIRGINIA_2014.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2014/VIRGINIA_2014.xlsx
@@ -2004,7 +2004,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C92">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C211">
@@ -4326,7 +4326,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C221">
@@ -9384,7 +9384,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C502">
@@ -10914,7 +10914,7 @@
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C587">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C588">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C615">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>Altzayanca</t>
+          <t>Atltzayanca</t>
         </is>
       </c>
       <c r="C883">
@@ -18582,7 +18582,7 @@
       </c>
       <c r="B1013" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C1013">
